--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount001.xlsx
@@ -752,8 +752,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -768,6 +771,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -780,6 +786,9 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -789,7 +798,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1150,294 +1159,294 @@
     <col min="2" max="2" width="11.3796296296296" customWidth="1"/>
     <col min="3" max="3" width="36.8796296296296" customWidth="1"/>
     <col min="4" max="6" width="10.8796296296296" customWidth="1"/>
-    <col min="7" max="7" width="27.25" customWidth="1"/>
-    <col min="8" max="8" width="25.1296296296296" customWidth="1"/>
+    <col min="7" max="7" width="27.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1296296296296" style="1" customWidth="1"/>
     <col min="9" max="10" width="15" customWidth="1"/>
     <col min="11" max="11" width="19.1296296296296" customWidth="1"/>
     <col min="12" max="12" width="33.75" customWidth="1"/>
-    <col min="13" max="13" width="33" customWidth="1"/>
+    <col min="13" max="13" width="33" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="43.2" spans="1:15">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
     </row>
     <row r="2" ht="15.6" spans="1:15">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
     </row>
     <row r="3" ht="15.6" spans="1:15">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
     </row>
     <row r="4" ht="15.6" spans="1:15">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
     </row>
     <row r="5" ht="15.6" spans="1:15">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
     </row>
     <row r="6" ht="15.6" spans="1:15">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
     </row>
     <row r="7" ht="15.6" spans="1:15">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
     </row>
     <row r="8" ht="15.6" spans="1:15">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
     </row>
     <row r="9" ht="15.6" spans="1:15">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
     </row>
     <row r="10" ht="15.6" spans="1:15">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
     </row>
     <row r="11" ht="15.6" spans="1:15">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
     </row>
     <row r="12" ht="15.6" spans="1:15">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
     </row>
     <row r="13" ht="15.6" spans="1:15">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
     </row>
     <row r="14" ht="15.6" spans="1:15">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
     </row>
     <row r="15" ht="15.6" spans="1:15">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\idea\ny\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -207,51 +207,48 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -560,41 +557,41 @@
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="11.36328125" customWidth="1"/>
-    <col min="3" max="3" width="36.90625" customWidth="1"/>
-    <col min="4" max="6" width="10.90625" customWidth="1"/>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="36.90625" style="1" customWidth="1"/>
+    <col min="4" max="6" width="10.90625" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.26953125" style="1" customWidth="1"/>
     <col min="8" max="8" width="25.08984375" style="1" customWidth="1"/>
-    <col min="9" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="19.08984375" customWidth="1"/>
+    <col min="9" max="10" width="15" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19.08984375" style="1" customWidth="1"/>
     <col min="12" max="12" width="33.7265625" customWidth="1"/>
     <col min="13" max="13" width="33" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="8" t="s">
@@ -606,31 +603,31 @@
       <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
     </row>
     <row r="2" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
       <c r="D2" s="11"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount001.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9420"/>
+    <workbookView windowWidth="18530" windowHeight="7130"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +28,6 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>此产品优惠调整（补充性）描述文字</t>
@@ -43,7 +37,6 @@
         <sz val="10.5"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（一产多费时必填、一费多产时不必填）</t>
@@ -59,10 +52,10 @@
     <t>优惠后费率</t>
   </si>
   <si>
-    <t>优惠起始时间（YYYY-MM-DD)</t>
+    <t>优惠起始时间</t>
   </si>
   <si>
-    <t>优惠截止时间（YYYY-MM-DD)</t>
+    <t>优惠截止时间</t>
   </si>
   <si>
     <t>本次优惠前费率</t>
@@ -78,7 +71,6 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>对此费率优惠调整（补充性）描述文字</t>
@@ -88,7 +80,6 @@
         <sz val="10.5"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（一费多产时必填、一产多费时不必填）</t>
@@ -101,8 +92,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,45 +111,177 @@
       <sz val="10.5"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -161,13 +290,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -177,8 +306,176 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -201,67 +498,356 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -548,112 +1134,114 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.36328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="36.90625" style="1" customWidth="1"/>
-    <col min="4" max="6" width="10.90625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="27.26953125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25.08984375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3636363636364" style="1" customWidth="1"/>
+    <col min="3" max="3" width="36.9090909090909" style="1" customWidth="1"/>
+    <col min="4" max="6" width="10.9090909090909" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27.2727272727273" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.0909090909091" style="1" customWidth="1"/>
     <col min="9" max="10" width="15" style="1" customWidth="1"/>
-    <col min="11" max="11" width="19.08984375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="33.7265625" customWidth="1"/>
+    <col min="11" max="11" width="19.0909090909091" style="1" customWidth="1"/>
+    <col min="12" max="12" width="33.7272727272727" customWidth="1"/>
     <col min="13" max="13" width="33" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" ht="40.5" spans="1:15">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
     </row>
-    <row r="2" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" spans="1:15">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
-      <c r="D2" s="11"/>
+      <c r="D2" s="8"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="6"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="14"/>
       <c r="M2" s="7"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount001.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18530" windowHeight="7130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18525" windowHeight="7125"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,8 @@
     </r>
   </si>
   <si>
-    <t>报告发布日期（YYYY-MM-DD)*</t>
+    <t>报告发布日期（YYYY/MM/DD)*</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -527,19 +528,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.36328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="36.90625" style="1" customWidth="1"/>
-    <col min="4" max="6" width="10.90625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="27.26953125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25.08984375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="33.7265625" customWidth="1"/>
+    <col min="2" max="2" width="11.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="36.875" style="1" customWidth="1"/>
+    <col min="4" max="6" width="10.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="33.75" customWidth="1"/>
     <col min="10" max="10" width="33" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -573,7 +574,7 @@
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
     </row>
-    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -597,7 +598,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -608,7 +609,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount001.xlsx
@@ -33,6 +33,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>此产品优惠调整（补充性）描述文字</t>
@@ -42,6 +43,7 @@
         <sz val="10.5"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（一产多费时必填、一费多产时不必填）</t>
@@ -67,6 +69,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>对此费率优惠调整（补充性）描述文字</t>
@@ -76,6 +79,7 @@
         <sz val="10.5"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（一费多产时必填、一产多费时不必填）</t>
@@ -102,34 +106,40 @@
       <sz val="10.5"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -183,7 +193,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -202,9 +212,6 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -214,13 +221,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -534,10 +550,10 @@
     <col min="2" max="2" width="11.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="36.875" style="1" customWidth="1"/>
     <col min="4" max="6" width="10.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="27.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27.25" style="13" customWidth="1"/>
+    <col min="8" max="8" width="25.125" style="13" customWidth="1"/>
     <col min="9" max="9" width="33.75" customWidth="1"/>
-    <col min="10" max="10" width="33" style="1" customWidth="1"/>
+    <col min="10" max="10" width="33" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
@@ -559,34 +575,34 @@
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
     </row>
     <row r="2" spans="1:12" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount001.xlsx
@@ -227,9 +227,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -238,6 +235,9 @@
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -550,10 +550,10 @@
     <col min="2" max="2" width="11.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="36.875" style="1" customWidth="1"/>
     <col min="4" max="6" width="10.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="27.25" style="13" customWidth="1"/>
-    <col min="8" max="8" width="25.125" style="13" customWidth="1"/>
+    <col min="7" max="7" width="27.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.125" style="1" customWidth="1"/>
     <col min="9" max="9" width="33.75" customWidth="1"/>
-    <col min="10" max="10" width="33" style="13" customWidth="1"/>
+    <col min="10" max="10" width="33" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
@@ -575,16 +575,16 @@
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="13" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9"/>
@@ -597,10 +597,10 @@
       <c r="D2" s="7"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
       <c r="I2" s="10"/>
-      <c r="J2" s="12"/>
+      <c r="J2" s="11"/>
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
     </row>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount001.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18525" windowHeight="7125"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18530" windowHeight="7130"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,27 +29,6 @@
     <t>子产品代码*</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>此产品优惠调整（补充性）描述文字</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（一产多费时必填、一费多产时不必填）</t>
-    </r>
-  </si>
-  <si>
     <t>优惠的费用*</t>
   </si>
   <si>
@@ -65,28 +44,15 @@
     <t>优惠截止时间</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>对此费率优惠调整（补充性）描述文字</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（一费多产时必填、一产多费时不必填）</t>
-    </r>
-  </si>
-  <si>
     <t>报告发布日期（YYYY/MM/DD)*</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>此产品优惠调整描述文字</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>对此费率优惠调整描述文字</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -544,19 +510,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="36.875" style="1" customWidth="1"/>
-    <col min="4" max="6" width="10.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="27.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="33.75" customWidth="1"/>
+    <col min="2" max="2" width="11.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="36.90625" style="1" customWidth="1"/>
+    <col min="4" max="6" width="10.90625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27.26953125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.08984375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="33.7265625" customWidth="1"/>
     <col min="10" max="10" width="33" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="25.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -564,33 +530,33 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="H1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="13" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>9</v>
       </c>
       <c r="K1" s="9"/>
       <c r="L1" s="9"/>
     </row>
-    <row r="2" spans="1:12" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -614,7 +580,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -625,7 +591,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount001.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18530" windowHeight="7130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18525" windowHeight="7125"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -48,12 +48,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>此产品优惠调整描述文字</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>对此费率优惠调整描述文字</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>单产品多费率描述文字</t>
+  </si>
+  <si>
+    <t>单费率多产品描述文字</t>
   </si>
 </sst>
 </file>
@@ -510,19 +508,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.36328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="36.90625" style="1" customWidth="1"/>
-    <col min="4" max="6" width="10.90625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="27.26953125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25.08984375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="33.7265625" customWidth="1"/>
+    <col min="2" max="2" width="11.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="36.875" style="1" customWidth="1"/>
+    <col min="4" max="6" width="10.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="33.75" customWidth="1"/>
     <col min="10" max="10" width="33" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -556,7 +554,7 @@
       <c r="K1" s="9"/>
       <c r="L1" s="9"/>
     </row>
-    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -580,7 +578,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -591,7 +589,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
